--- a/data/research_results/european_energy_dashboard.xlsx
+++ b/data/research_results/european_energy_dashboard.xlsx
@@ -3257,7 +3257,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-11T02:08:11.449386+00:00</t>
+          <t>2026-03-11T02:59:23.306269+00:00</t>
         </is>
       </c>
     </row>
